--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AEDEEF-EB9C-4272-A616-A8756115C961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E251348E-325F-43B6-8E3F-B0E7520742CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="571">
   <si>
     <t>NAZWA</t>
   </si>
@@ -1737,6 +1737,9 @@
   </si>
   <si>
     <t>CWI-0113</t>
+  </si>
+  <si>
+    <t>STRENGTH AND STRETCH - Spider Stretch</t>
   </si>
 </sst>
 </file>
@@ -1937,24 +1940,6 @@
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -2161,6 +2146,24 @@
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2175,18 +2178,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela5" displayName="Tabela5" ref="A1:I114" totalsRowShown="0" headerRowDxfId="0" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela5" displayName="Tabela5" ref="A1:I114" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:I114" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NAZWA" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="KATEGORIA" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="POZIOM" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TAGI" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="OPIS" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="LINK" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DATA" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="YT" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ID" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NAZWA" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="KATEGORIA" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="POZIOM" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TAGI" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="OPIS" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="LINK" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="YT" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ID" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5354,7 +5357,7 @@
     </row>
     <row r="114" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="18" t="s">
-        <v>218</v>
+        <v>570</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>219</v>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E251348E-325F-43B6-8E3F-B0E7520742CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F3B62-4813-449B-8840-FD151AC622C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="582">
   <si>
     <t>NAZWA</t>
   </si>
@@ -1740,6 +1740,39 @@
   </si>
   <si>
     <t>STRENGTH AND STRETCH - Spider Stretch</t>
+  </si>
+  <si>
+    <t>Synchronizacja, Skale, Niezależność palców, Lewa ręka, Bursty</t>
+  </si>
+  <si>
+    <t>Dzięki temu ćwiczeniu nauczysz się płynnie poruszać po najczęściej spotykanych opalcowaniach skal. Dodatkowo z czasem wyeliminujesz problem podskakującej kostki (tzw. dziobaka).</t>
+  </si>
+  <si>
+    <t>CWI-0114</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo Strada A</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PWQc5gjDnih_E_Cre6cQlzdOqfzgdxQo&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Bg8h4akwXsyTTikIhCZz5K96VpeGeg1S&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>CWI-0115</t>
+  </si>
+  <si>
+    <t>CWI-0116</t>
+  </si>
+  <si>
+    <t>Ćwiczenie na wszystkie opalcowania skali wzdłuż jednej struny. Bursty Triolowe z kierunkiem dźwięków do przodu.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie na wszystkie opalcowania skali wzdłuż jednej struny. Bursty Triolowe z kierunkiem dźwięków do tyłu.</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo Strada B</t>
   </si>
 </sst>
 </file>
@@ -1811,7 +1844,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1827,6 +1860,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -1858,7 +1897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1866,28 +1905,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1900,12 +1925,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1934,6 +1953,36 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1941,8 +1990,8 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1953,17 +2002,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1976,17 +2019,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1999,17 +2036,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2022,17 +2053,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2045,17 +2070,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2068,17 +2087,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2091,17 +2104,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2114,17 +2121,11 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -2135,19 +2136,14 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2156,12 +2152,6 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -2414,2995 +2404,3078 @@
   <dimension ref="A1:K122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="37.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="60" style="6" customWidth="1"/>
-    <col min="6" max="6" width="54" style="6" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="51.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="14" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="35" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="60" style="10" customWidth="1"/>
+    <col min="6" max="6" width="54" style="10" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="51.7109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="14" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="13" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11" t="s">
+      <c r="G2" s="25"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="13" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="11" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11" t="s">
+      <c r="G4" s="25"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="13" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="11" t="s">
+      <c r="G5" s="25"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="13" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="11" t="s">
+      <c r="G6" s="25"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="13" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11" t="s">
+      <c r="G7" s="25"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="13" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11" t="s">
+      <c r="G8" s="25"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="13" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11" t="s">
+      <c r="G9" s="25"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="13" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11" t="s">
+      <c r="G10" s="25"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="13" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11" t="s">
+      <c r="G11" s="25"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="13" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="11" t="s">
+      <c r="G12" s="25"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="13" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="11" t="s">
+      <c r="G13" s="25"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="13" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="11" t="s">
+      <c r="G14" s="25"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11" t="s">
+      <c r="G15" s="25"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="13" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10" t="s">
+      <c r="G16" s="25"/>
+      <c r="H16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="13" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="11" t="s">
+      <c r="G17" s="25"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="13" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="11" t="s">
+      <c r="G18" s="25"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="13" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="11" t="s">
+      <c r="G19" s="25"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="13" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="11" t="s">
+      <c r="G20" s="25"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="13" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="11" t="s">
+      <c r="G21" s="25"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="13" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10" t="s">
+      <c r="G22" s="25"/>
+      <c r="H22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="13" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10" t="s">
+      <c r="G23" s="25"/>
+      <c r="H23" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="13" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="10" t="s">
+      <c r="G24" s="25"/>
+      <c r="H24" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="13" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="13" t="s">
+      <c r="G25" s="25"/>
+      <c r="H25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="13" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="11" t="s">
+      <c r="G26" s="25"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="13" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="11" t="s">
+      <c r="G27" s="25"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="13" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="10" t="s">
+      <c r="G28" s="25"/>
+      <c r="H28" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="13" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="11" t="s">
+      <c r="G29" s="25"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="13" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="11" t="s">
+      <c r="G30" s="25"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="13" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="11" t="s">
+      <c r="G31" s="25"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="13" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="11" t="s">
+      <c r="G32" s="25"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="13" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="11" t="s">
+      <c r="G33" s="25"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="13" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="11" t="s">
+      <c r="G34" s="25"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="13" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="13" t="s">
+      <c r="G35" s="25"/>
+      <c r="H35" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="13" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="10" t="s">
+      <c r="G36" s="25"/>
+      <c r="H36" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="13" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10" t="s">
+      <c r="G37" s="25"/>
+      <c r="H37" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="13" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="11" t="s">
+      <c r="G38" s="25"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="13" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="11" t="s">
+      <c r="G39" s="25"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="13" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="11" t="s">
+      <c r="G40" s="25"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="13" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G41" s="9"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="11" t="s">
+      <c r="G41" s="25"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="13" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="11" t="s">
+      <c r="G42" s="25"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="13" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="11" t="s">
+      <c r="G43" s="25"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="13" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="11" t="s">
+      <c r="G44" s="25"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="13" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="11" t="s">
+      <c r="G45" s="25"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="13" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="11" t="s">
+      <c r="G46" s="25"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="13" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G47" s="9"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="11" t="s">
+      <c r="G47" s="25"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="13" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="G48" s="9"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="11" t="s">
+      <c r="G48" s="25"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="13" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G49" s="9"/>
-      <c r="H49" s="10" t="s">
+      <c r="G49" s="25"/>
+      <c r="H49" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="13" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="G50" s="9"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="11" t="s">
+      <c r="G50" s="25"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="13" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G51" s="9"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="11" t="s">
+      <c r="G51" s="25"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="13" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G52" s="9"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="11" t="s">
+      <c r="G52" s="25"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="13" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="11" t="s">
+      <c r="G53" s="25"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="13" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="F54" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="11" t="s">
+      <c r="G54" s="25"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="13" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="F55" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G55" s="9"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="11" t="s">
+      <c r="G55" s="25"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="13" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="F56" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="11" t="s">
+      <c r="G56" s="25"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="13" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F57" s="13" t="s">
+      <c r="F57" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="G57" s="9"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="11" t="s">
+      <c r="G57" s="25"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="13" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="F58" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="26">
         <v>46246</v>
       </c>
-      <c r="H58" s="10"/>
-      <c r="I58" s="11" t="s">
+      <c r="H58" s="5"/>
+      <c r="I58" s="13" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="G59" s="9"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="11" t="s">
+      <c r="G59" s="25"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="13" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G60" s="9"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="11" t="s">
+      <c r="G60" s="25"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="13" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G61" s="9"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="11" t="s">
+      <c r="G61" s="25"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="13" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="G62" s="9"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="11" t="s">
+      <c r="G62" s="25"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="13" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="F63" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G63" s="9"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="11" t="s">
+      <c r="G63" s="25"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="13" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="F64" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G64" s="9"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="11" t="s">
+      <c r="G64" s="25"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="13" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="F65" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="G65" s="9"/>
-      <c r="H65" s="13" t="s">
+      <c r="G65" s="25"/>
+      <c r="H65" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="13" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G66" s="9"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="11" t="s">
+      <c r="G66" s="25"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="13" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="G67" s="9"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="11" t="s">
+      <c r="G67" s="25"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="13" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="G68" s="9"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="11" t="s">
+      <c r="G68" s="25"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="13" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G69" s="9"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="11" t="s">
+      <c r="G69" s="25"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="13" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G70" s="9"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="11" t="s">
+      <c r="G70" s="25"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="13" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="G71" s="9"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="11" t="s">
+      <c r="G71" s="25"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="13" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="F72" s="12" t="s">
+      <c r="F72" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G72" s="9"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="11" t="s">
+      <c r="G72" s="25"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="13" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F73" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="G73" s="9"/>
-      <c r="H73" s="10" t="s">
+      <c r="G73" s="25"/>
+      <c r="H73" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="13" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F74" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="G74" s="17">
+      <c r="G74" s="27">
         <v>46238</v>
       </c>
-      <c r="H74" s="10"/>
-      <c r="I74" s="11" t="s">
+      <c r="H74" s="5"/>
+      <c r="I74" s="13" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="12" t="s">
+      <c r="F75" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G75" s="17">
+      <c r="G75" s="27">
         <v>46238</v>
       </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="11" t="s">
+      <c r="H75" s="5"/>
+      <c r="I75" s="13" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="F76" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="G76" s="17">
+      <c r="G76" s="27">
         <v>46238</v>
       </c>
-      <c r="H76" s="10"/>
-      <c r="I76" s="11" t="s">
+      <c r="H76" s="5"/>
+      <c r="I76" s="13" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F77" s="12" t="s">
+      <c r="F77" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G77" s="17">
+      <c r="G77" s="27">
         <v>46238</v>
       </c>
-      <c r="H77" s="10"/>
-      <c r="I77" s="11" t="s">
+      <c r="H77" s="5"/>
+      <c r="I77" s="13" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="F78" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="G78" s="17">
+      <c r="G78" s="27">
         <v>46238</v>
       </c>
-      <c r="H78" s="10"/>
-      <c r="I78" s="11" t="s">
+      <c r="H78" s="5"/>
+      <c r="I78" s="13" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="F79" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="G79" s="17">
+      <c r="G79" s="27">
         <v>46238</v>
       </c>
-      <c r="H79" s="10"/>
-      <c r="I79" s="11" t="s">
+      <c r="H79" s="5"/>
+      <c r="I79" s="13" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F80" s="8" t="s">
+      <c r="F80" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G80" s="17">
+      <c r="G80" s="27">
         <v>46239</v>
       </c>
-      <c r="H80" s="10"/>
-      <c r="I80" s="11" t="s">
+      <c r="H80" s="5"/>
+      <c r="I80" s="13" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="F81" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G81" s="17">
+      <c r="G81" s="27">
         <v>46239</v>
       </c>
-      <c r="H81" s="10"/>
-      <c r="I81" s="11" t="s">
+      <c r="H81" s="5"/>
+      <c r="I81" s="13" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="F82" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="G82" s="17">
+      <c r="G82" s="27">
         <v>46239</v>
       </c>
-      <c r="H82" s="10"/>
-      <c r="I82" s="11" t="s">
+      <c r="H82" s="5"/>
+      <c r="I82" s="13" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="F83" s="12" t="s">
+      <c r="F83" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G83" s="17">
+      <c r="G83" s="27">
         <v>46239</v>
       </c>
-      <c r="H83" s="10"/>
-      <c r="I83" s="11" t="s">
+      <c r="H83" s="5"/>
+      <c r="I83" s="13" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="F84" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G84" s="17">
+      <c r="G84" s="27">
         <v>46239</v>
       </c>
-      <c r="H84" s="10"/>
-      <c r="I84" s="11" t="s">
+      <c r="H84" s="5"/>
+      <c r="I84" s="13" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
+      <c r="A85" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="F85" s="12" t="s">
+      <c r="F85" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G85" s="17">
+      <c r="G85" s="27">
         <v>46239</v>
       </c>
-      <c r="H85" s="10"/>
-      <c r="I85" s="11" t="s">
+      <c r="H85" s="5"/>
+      <c r="I85" s="13" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
+      <c r="A86" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="F86" s="12" t="s">
+      <c r="F86" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G86" s="9"/>
-      <c r="H86" s="10"/>
-      <c r="I86" s="11" t="s">
+      <c r="G86" s="25"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="13" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="F87" s="12" t="s">
+      <c r="F87" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="G87" s="9"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="11" t="s">
+      <c r="G87" s="25"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="13" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="F88" s="12" t="s">
+      <c r="F88" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G88" s="9"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="11" t="s">
+      <c r="G88" s="25"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="13" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="F89" s="12" t="s">
+      <c r="F89" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="G89" s="17">
+      <c r="G89" s="27">
         <v>46240</v>
       </c>
-      <c r="H89" s="10"/>
-      <c r="I89" s="11" t="s">
+      <c r="H89" s="5"/>
+      <c r="I89" s="13" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="F90" s="12" t="s">
+      <c r="F90" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G90" s="17">
+      <c r="G90" s="27">
         <v>46240</v>
       </c>
-      <c r="H90" s="10"/>
-      <c r="I90" s="11" t="s">
+      <c r="H90" s="5"/>
+      <c r="I90" s="13" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="F91" s="12" t="s">
+      <c r="F91" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="G91" s="17">
+      <c r="G91" s="27">
         <v>46240</v>
       </c>
-      <c r="H91" s="10"/>
-      <c r="I91" s="11" t="s">
+      <c r="H91" s="5"/>
+      <c r="I91" s="13" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="D92" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F92" s="12" t="s">
+      <c r="F92" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="G92" s="17">
+      <c r="G92" s="27">
         <v>46240</v>
       </c>
-      <c r="H92" s="10"/>
-      <c r="I92" s="11" t="s">
+      <c r="H92" s="5"/>
+      <c r="I92" s="13" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="D93" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="F93" s="12" t="s">
+      <c r="F93" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G93" s="17">
+      <c r="G93" s="27">
         <v>46240</v>
       </c>
-      <c r="H93" s="10"/>
-      <c r="I93" s="11" t="s">
+      <c r="H93" s="5"/>
+      <c r="I93" s="13" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="D94" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F94" s="12" t="s">
+      <c r="F94" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="G94" s="17">
+      <c r="G94" s="27">
         <v>46240</v>
       </c>
-      <c r="H94" s="10"/>
-      <c r="I94" s="11" t="s">
+      <c r="H94" s="5"/>
+      <c r="I94" s="13" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="D95" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="F95" s="12" t="s">
+      <c r="F95" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G95" s="17">
+      <c r="G95" s="27">
         <v>46240</v>
       </c>
-      <c r="H95" s="10"/>
-      <c r="I95" s="11" t="s">
+      <c r="H95" s="5"/>
+      <c r="I95" s="13" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C96" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F96" s="12" t="s">
+      <c r="F96" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="G96" s="17">
+      <c r="G96" s="27">
         <v>46240</v>
       </c>
-      <c r="H96" s="10"/>
-      <c r="I96" s="11" t="s">
+      <c r="H96" s="5"/>
+      <c r="I96" s="13" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="F97" s="12" t="s">
+      <c r="F97" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G97" s="17">
+      <c r="G97" s="27">
         <v>46240</v>
       </c>
-      <c r="H97" s="10"/>
-      <c r="I97" s="11" t="s">
+      <c r="H97" s="5"/>
+      <c r="I97" s="13" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F98" s="12" t="s">
+      <c r="F98" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="G98" s="17">
+      <c r="G98" s="27">
         <v>46240</v>
       </c>
-      <c r="H98" s="10"/>
-      <c r="I98" s="11" t="s">
+      <c r="H98" s="5"/>
+      <c r="I98" s="13" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C99" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D99" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E99" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F99" s="12" t="s">
+      <c r="F99" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="G99" s="17">
+      <c r="G99" s="27">
         <v>46240</v>
       </c>
-      <c r="H99" s="10"/>
-      <c r="I99" s="11" t="s">
+      <c r="H99" s="5"/>
+      <c r="I99" s="13" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="F100" s="12" t="s">
+      <c r="F100" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="G100" s="17">
+      <c r="G100" s="27">
         <v>46240</v>
       </c>
-      <c r="H100" s="10"/>
-      <c r="I100" s="11" t="s">
+      <c r="H100" s="5"/>
+      <c r="I100" s="13" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="F101" s="12" t="s">
+      <c r="F101" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="G101" s="17">
+      <c r="G101" s="27">
         <v>46240</v>
       </c>
-      <c r="H101" s="10"/>
-      <c r="I101" s="11" t="s">
+      <c r="H101" s="5"/>
+      <c r="I101" s="13" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="F102" s="12" t="s">
+      <c r="F102" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="G102" s="17">
+      <c r="G102" s="27">
         <v>46240</v>
       </c>
-      <c r="H102" s="10"/>
-      <c r="I102" s="11" t="s">
+      <c r="H102" s="5"/>
+      <c r="I102" s="13" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="F103" s="12" t="s">
+      <c r="F103" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="G103" s="17">
+      <c r="G103" s="27">
         <v>46240</v>
       </c>
-      <c r="H103" s="10"/>
-      <c r="I103" s="11" t="s">
+      <c r="H103" s="5"/>
+      <c r="I103" s="13" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F104" s="12" t="s">
+      <c r="F104" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G104" s="17">
+      <c r="G104" s="27">
         <v>46240</v>
       </c>
-      <c r="H104" s="10"/>
-      <c r="I104" s="11" t="s">
+      <c r="H104" s="5"/>
+      <c r="I104" s="13" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="C105" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="E105" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="F105" s="12" t="s">
+      <c r="F105" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="G105" s="17">
+      <c r="G105" s="27">
         <v>46240</v>
       </c>
-      <c r="H105" s="10"/>
-      <c r="I105" s="11" t="s">
+      <c r="H105" s="5"/>
+      <c r="I105" s="13" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E106" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F106" s="12" t="s">
+      <c r="F106" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G106" s="17">
+      <c r="G106" s="27">
         <v>46240</v>
       </c>
-      <c r="H106" s="10"/>
-      <c r="I106" s="11" t="s">
+      <c r="H106" s="5"/>
+      <c r="I106" s="13" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E107" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="F107" s="12" t="s">
+      <c r="F107" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="G107" s="17">
+      <c r="G107" s="27">
         <v>46240</v>
       </c>
-      <c r="H107" s="10"/>
-      <c r="I107" s="11" t="s">
+      <c r="H107" s="5"/>
+      <c r="I107" s="13" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F108" s="12" t="s">
+      <c r="F108" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="G108" s="17">
+      <c r="G108" s="27">
         <v>46240</v>
       </c>
-      <c r="H108" s="10"/>
-      <c r="I108" s="11" t="s">
+      <c r="H108" s="5"/>
+      <c r="I108" s="13" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="C109" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="F109" s="12" t="s">
+      <c r="F109" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="G109" s="17">
+      <c r="G109" s="27">
         <v>46240</v>
       </c>
-      <c r="H109" s="10"/>
-      <c r="I109" s="11" t="s">
+      <c r="H109" s="5"/>
+      <c r="I109" s="13" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E110" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F110" s="12" t="s">
+      <c r="F110" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="G110" s="17">
+      <c r="G110" s="27">
         <v>46240</v>
       </c>
-      <c r="H110" s="10"/>
-      <c r="I110" s="11" t="s">
+      <c r="H110" s="5"/>
+      <c r="I110" s="13" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E111" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="F111" s="12" t="s">
+      <c r="F111" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="G111" s="17">
+      <c r="G111" s="27">
         <v>46240</v>
       </c>
-      <c r="H111" s="10"/>
-      <c r="I111" s="11" t="s">
+      <c r="H111" s="5"/>
+      <c r="I111" s="13" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="E112" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="F112" s="12" t="s">
+      <c r="F112" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="G112" s="17">
+      <c r="G112" s="27">
         <v>46240</v>
       </c>
-      <c r="H112" s="10"/>
-      <c r="I112" s="11" t="s">
+      <c r="H112" s="5"/>
+      <c r="I112" s="13" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
+      <c r="A113" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="E113" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="F113" s="12" t="s">
+      <c r="F113" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G113" s="17">
+      <c r="G113" s="27">
         <v>46240</v>
       </c>
-      <c r="H113" s="10"/>
-      <c r="I113" s="11" t="s">
+      <c r="H113" s="5"/>
+      <c r="I113" s="13" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="18" t="s">
+      <c r="A114" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D114" s="18" t="s">
+      <c r="D114" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E114" s="18" t="s">
+      <c r="E114" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="F114" s="19" t="s">
+      <c r="F114" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="G114" s="20">
+      <c r="G114" s="12">
         <v>46325</v>
       </c>
-      <c r="H114" s="18"/>
-      <c r="I114" s="21" t="s">
+      <c r="I114" s="13" t="s">
         <v>569</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C115" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="E115" s="28" t="s">
+        <v>572</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="G115" s="21">
+        <v>46325</v>
+      </c>
+      <c r="I115" s="22" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C116" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="G116" s="21">
+        <v>46325</v>
+      </c>
+      <c r="H116" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I116" s="22" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C117" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="G117" s="21">
+        <v>46325</v>
+      </c>
+      <c r="H117" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I117" s="22" t="s">
+        <v>578</v>
+      </c>
+    </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C118" s="22"/>
-      <c r="D118" s="23"/>
-      <c r="E118" s="23"/>
-      <c r="F118" s="22"/>
-      <c r="G118" s="22"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="22"/>
-      <c r="K118" s="26"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="16"/>
+      <c r="I118" s="17"/>
+      <c r="J118" s="14"/>
+      <c r="K118" s="18"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C122" s="22"/>
-      <c r="D122" s="23"/>
-      <c r="E122" s="23"/>
-      <c r="F122" s="22"/>
-      <c r="G122" s="22"/>
-      <c r="H122" s="24"/>
-      <c r="I122" s="25"/>
-      <c r="J122" s="22"/>
-      <c r="K122" s="26"/>
+      <c r="C122" s="14"/>
+      <c r="D122" s="15"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14"/>
+      <c r="H122" s="16"/>
+      <c r="I122" s="17"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - ĆWICZENIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F3B62-4813-449B-8840-FD151AC622C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB9D496-782F-4E33-A8FD-DAE2E21AFB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="577">
   <si>
     <t>NAZWA</t>
   </si>
@@ -488,18 +488,6 @@
   </si>
   <si>
     <t>https://youtu.be/-zkjiVzygQI?si=7-lBNOvzQcHifIiu</t>
-  </si>
-  <si>
-    <t>SHRED - Shredo-Strada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shred, Alternate Picking, Skale, Synchronizacja, Lewa Ręka, Speed Burst, Niezależność palców, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">To ćwiczenie, dzięki któremu zbudujesz szybkość gry. Jest grane na jednej strunie oraz zawiera "speed burst". Koniecznie graj w pełnym rozluźnieniu, tylko jednym palcem na raz. </t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1SyWnVmYzR643V9ggK8Z_jE7fUrH83CDT&amp;usp=drive_fs</t>
   </si>
   <si>
     <t>https://youtu.be/Nb-BfXzdX7U?si=6-PedbFAR3YJA2_l</t>
@@ -1497,9 +1485,6 @@
   </si>
   <si>
     <t>CWI-0035</t>
-  </si>
-  <si>
-    <t>CWI-0036</t>
   </si>
   <si>
     <t>CWI-0037</t>
@@ -2168,8 +2153,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela5" displayName="Tabela5" ref="A1:I114" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I114" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela5" displayName="Tabela5" ref="A1:I113" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NAZWA" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="KATEGORIA" dataDxfId="7"/>
@@ -2401,7 +2386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="10" customWidth="1"/>
@@ -2442,7 +2427,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2467,7 +2452,7 @@
       <c r="G2" s="25"/>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2492,7 +2477,7 @@
       <c r="G3" s="25"/>
       <c r="H3" s="5"/>
       <c r="I3" s="13" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2517,7 +2502,7 @@
       <c r="G4" s="25"/>
       <c r="H4" s="5"/>
       <c r="I4" s="13" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2542,7 +2527,7 @@
       <c r="G5" s="25"/>
       <c r="H5" s="5"/>
       <c r="I5" s="13" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2567,7 +2552,7 @@
       <c r="G6" s="25"/>
       <c r="H6" s="5"/>
       <c r="I6" s="13" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2592,7 +2577,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="5"/>
       <c r="I7" s="13" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,7 +2602,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="5"/>
       <c r="I8" s="13" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2642,7 +2627,7 @@
       <c r="G9" s="25"/>
       <c r="H9" s="5"/>
       <c r="I9" s="13" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2667,7 +2652,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="5"/>
       <c r="I10" s="13" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2692,7 +2677,7 @@
       <c r="G11" s="25"/>
       <c r="H11" s="5"/>
       <c r="I11" s="13" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2717,7 +2702,7 @@
       <c r="G12" s="25"/>
       <c r="H12" s="5"/>
       <c r="I12" s="13" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2742,7 +2727,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="5"/>
       <c r="I13" s="13" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2767,7 +2752,7 @@
       <c r="G14" s="25"/>
       <c r="H14" s="5"/>
       <c r="I14" s="13" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2792,7 +2777,7 @@
       <c r="G15" s="25"/>
       <c r="H15" s="5"/>
       <c r="I15" s="13" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2819,7 +2804,7 @@
         <v>74</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2844,7 +2829,7 @@
       <c r="G17" s="25"/>
       <c r="H17" s="5"/>
       <c r="I17" s="13" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2869,7 +2854,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="5"/>
       <c r="I18" s="13" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2894,7 +2879,7 @@
       <c r="G19" s="25"/>
       <c r="H19" s="5"/>
       <c r="I19" s="13" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2919,7 +2904,7 @@
       <c r="G20" s="25"/>
       <c r="H20" s="5"/>
       <c r="I20" s="13" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2944,7 +2929,7 @@
       <c r="G21" s="25"/>
       <c r="H21" s="5"/>
       <c r="I21" s="13" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2971,7 +2956,7 @@
         <v>100</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2998,7 +2983,7 @@
         <v>100</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3025,7 +3010,7 @@
         <v>100</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3052,7 +3037,7 @@
         <v>110</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3077,7 +3062,7 @@
       <c r="G26" s="25"/>
       <c r="H26" s="5"/>
       <c r="I26" s="13" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3102,7 +3087,7 @@
       <c r="G27" s="25"/>
       <c r="H27" s="5"/>
       <c r="I27" s="13" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3129,7 +3114,7 @@
         <v>123</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3154,7 +3139,7 @@
       <c r="G29" s="25"/>
       <c r="H29" s="5"/>
       <c r="I29" s="13" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3179,7 +3164,7 @@
       <c r="G30" s="25"/>
       <c r="H30" s="5"/>
       <c r="I30" s="13" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3204,7 +3189,7 @@
       <c r="G31" s="25"/>
       <c r="H31" s="5"/>
       <c r="I31" s="13" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3229,7 +3214,7 @@
       <c r="G32" s="25"/>
       <c r="H32" s="5"/>
       <c r="I32" s="13" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3254,7 +3239,7 @@
       <c r="G33" s="25"/>
       <c r="H33" s="5"/>
       <c r="I33" s="13" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3279,7 +3264,7 @@
       <c r="G34" s="25"/>
       <c r="H34" s="5"/>
       <c r="I34" s="13" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3306,7 +3291,7 @@
         <v>148</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3333,12 +3318,12 @@
         <v>153</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>133</v>
@@ -3347,20 +3332,18 @@
         <v>15</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G37" s="25"/>
-      <c r="H37" s="5" t="s">
-        <v>158</v>
-      </c>
+      <c r="H37" s="5"/>
       <c r="I37" s="13" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3374,23 +3357,23 @@
         <v>15</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="5"/>
       <c r="I38" s="13" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>133</v>
@@ -3399,23 +3382,23 @@
         <v>15</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="G39" s="25"/>
       <c r="H39" s="5"/>
       <c r="I39" s="13" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>133</v>
@@ -3424,23 +3407,23 @@
         <v>15</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="G40" s="25"/>
       <c r="H40" s="5"/>
       <c r="I40" s="13" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>133</v>
@@ -3449,7 +3432,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>170</v>
@@ -3460,7 +3443,7 @@
       <c r="G41" s="25"/>
       <c r="H41" s="5"/>
       <c r="I41" s="13" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3485,7 +3468,7 @@
       <c r="G42" s="25"/>
       <c r="H42" s="5"/>
       <c r="I42" s="13" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3510,7 +3493,7 @@
       <c r="G43" s="25"/>
       <c r="H43" s="5"/>
       <c r="I43" s="13" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3518,35 +3501,35 @@
         <v>180</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G44" s="25"/>
       <c r="H44" s="5"/>
       <c r="I44" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>186</v>
@@ -3554,13 +3537,13 @@
       <c r="E45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="4" t="s">
         <v>188</v>
       </c>
       <c r="G45" s="25"/>
       <c r="H45" s="5"/>
       <c r="I45" s="13" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3568,10 +3551,10 @@
         <v>189</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>190</v>
@@ -3579,13 +3562,13 @@
       <c r="E46" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>192</v>
       </c>
       <c r="G46" s="25"/>
       <c r="H46" s="5"/>
       <c r="I46" s="13" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3593,7 +3576,7 @@
         <v>193</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>37</v>
@@ -3610,7 +3593,7 @@
       <c r="G47" s="25"/>
       <c r="H47" s="5"/>
       <c r="I47" s="13" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,10 +3601,10 @@
         <v>197</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>198</v>
@@ -3633,36 +3616,36 @@
         <v>200</v>
       </c>
       <c r="G48" s="25"/>
-      <c r="H48" s="5"/>
+      <c r="H48" s="5" t="s">
+        <v>201</v>
+      </c>
       <c r="I48" s="13" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G49" s="25"/>
-      <c r="H49" s="5" t="s">
-        <v>205</v>
-      </c>
+      <c r="H49" s="5"/>
       <c r="I49" s="13" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3670,10 +3653,10 @@
         <v>206</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>207</v>
@@ -3687,7 +3670,7 @@
       <c r="G50" s="25"/>
       <c r="H50" s="5"/>
       <c r="I50" s="13" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3695,10 +3678,10 @@
         <v>210</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>211</v>
@@ -3712,7 +3695,7 @@
       <c r="G51" s="25"/>
       <c r="H51" s="5"/>
       <c r="I51" s="13" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3720,60 +3703,60 @@
         <v>214</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G52" s="25"/>
       <c r="H52" s="5"/>
       <c r="I52" s="13" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G53" s="25"/>
       <c r="H53" s="5"/>
       <c r="I53" s="13" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>225</v>
@@ -3787,7 +3770,7 @@
       <c r="G54" s="25"/>
       <c r="H54" s="5"/>
       <c r="I54" s="13" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3795,35 +3778,35 @@
         <v>228</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>15</v>
+        <v>229</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G55" s="25"/>
       <c r="H55" s="5"/>
       <c r="I55" s="13" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>233</v>
+        <v>10</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>234</v>
@@ -3831,65 +3814,65 @@
       <c r="E56" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="7" t="s">
         <v>236</v>
       </c>
       <c r="G56" s="25"/>
       <c r="H56" s="5"/>
       <c r="I56" s="13" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="8" t="s">
         <v>237</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="D57" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="E57" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="G57" s="25"/>
+      <c r="F57" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G57" s="26">
+        <v>46246</v>
+      </c>
       <c r="H57" s="5"/>
       <c r="I57" s="13" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
-        <v>241</v>
+      <c r="A58" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D58" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G58" s="26">
-        <v>46246</v>
-      </c>
+      <c r="G58" s="25"/>
       <c r="H58" s="5"/>
       <c r="I58" s="13" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3897,7 +3880,7 @@
         <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>10</v>
@@ -3908,13 +3891,13 @@
       <c r="E59" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="6" t="s">
         <v>249</v>
       </c>
       <c r="G59" s="25"/>
       <c r="H59" s="5"/>
       <c r="I59" s="13" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3922,32 +3905,32 @@
         <v>250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G60" s="25"/>
       <c r="H60" s="5"/>
       <c r="I60" s="13" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -3964,7 +3947,7 @@
       <c r="G61" s="25"/>
       <c r="H61" s="5"/>
       <c r="I61" s="13" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3972,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
@@ -3989,7 +3972,7 @@
       <c r="G62" s="25"/>
       <c r="H62" s="5"/>
       <c r="I62" s="13" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3997,87 +3980,87 @@
         <v>263</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="G63" s="25"/>
       <c r="H63" s="5"/>
       <c r="I63" s="13" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G64" s="25"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="I64" s="13" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G65" s="25"/>
-      <c r="H65" s="7" t="s">
-        <v>275</v>
-      </c>
+      <c r="H65" s="5"/>
       <c r="I65" s="13" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>278</v>
@@ -4085,13 +4068,13 @@
       <c r="E66" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="4" t="s">
         <v>280</v>
       </c>
       <c r="G66" s="25"/>
       <c r="H66" s="5"/>
       <c r="I66" s="13" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4099,10 +4082,10 @@
         <v>281</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>282</v>
@@ -4110,13 +4093,13 @@
       <c r="E67" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="6" t="s">
         <v>284</v>
       </c>
       <c r="G67" s="25"/>
       <c r="H67" s="5"/>
       <c r="I67" s="13" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4124,10 +4107,10 @@
         <v>285</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>286</v>
@@ -4141,7 +4124,7 @@
       <c r="G68" s="25"/>
       <c r="H68" s="5"/>
       <c r="I68" s="13" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4149,10 +4132,10 @@
         <v>289</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>290</v>
@@ -4166,7 +4149,7 @@
       <c r="G69" s="25"/>
       <c r="H69" s="5"/>
       <c r="I69" s="13" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4174,7 +4157,7 @@
         <v>293</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>15</v>
@@ -4191,7 +4174,7 @@
       <c r="G70" s="25"/>
       <c r="H70" s="5"/>
       <c r="I70" s="13" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4199,10 +4182,10 @@
         <v>297</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>298</v>
@@ -4216,7 +4199,7 @@
       <c r="G71" s="25"/>
       <c r="H71" s="5"/>
       <c r="I71" s="13" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4224,213 +4207,215 @@
         <v>301</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G72" s="25"/>
-      <c r="H72" s="5"/>
+      <c r="H72" s="5" t="s">
+        <v>306</v>
+      </c>
       <c r="I72" s="13" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>306</v>
+        <v>118</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G73" s="25"/>
-      <c r="H73" s="5" t="s">
-        <v>310</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G73" s="27">
+        <v>46238</v>
+      </c>
+      <c r="H73" s="5"/>
       <c r="I73" s="13" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="F74" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>315</v>
       </c>
       <c r="G74" s="27">
         <v>46238</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="13" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E75" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F75" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>318</v>
       </c>
       <c r="G75" s="27">
         <v>46238</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="13" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>312</v>
+        <v>37</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F76" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="G76" s="27">
         <v>46238</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="13" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E77" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F77" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="G77" s="27">
         <v>46238</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="13" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E78" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F78" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="G78" s="27">
         <v>46238</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="13" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="4" t="s">
         <v>330</v>
       </c>
       <c r="G79" s="27">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="13" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4441,109 +4426,109 @@
         <v>118</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="F80" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="G80" s="27">
         <v>46239</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="13" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E81" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F81" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="G81" s="27">
         <v>46239</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="13" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E82" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F82" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="G82" s="27">
         <v>46239</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="13" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E83" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F83" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="G83" s="27">
         <v>46239</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="13" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>118</v>
@@ -4552,34 +4537,34 @@
         <v>15</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E84" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F84" s="6" t="s">
         <v>345</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>346</v>
       </c>
       <c r="G84" s="27">
         <v>46239</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="13" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>348</v>
@@ -4587,12 +4572,10 @@
       <c r="F85" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G85" s="27">
-        <v>46239</v>
-      </c>
+      <c r="G85" s="25"/>
       <c r="H85" s="5"/>
       <c r="I85" s="13" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4600,10 +4583,10 @@
         <v>350</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>351</v>
@@ -4617,7 +4600,7 @@
       <c r="G86" s="25"/>
       <c r="H86" s="5"/>
       <c r="I86" s="13" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4625,10 +4608,10 @@
         <v>354</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>355</v>
@@ -4642,7 +4625,7 @@
       <c r="G87" s="25"/>
       <c r="H87" s="5"/>
       <c r="I87" s="13" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4650,10 +4633,10 @@
         <v>358</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>359</v>
@@ -4664,10 +4647,12 @@
       <c r="F88" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G88" s="25"/>
+      <c r="G88" s="27">
+        <v>46240</v>
+      </c>
       <c r="H88" s="5"/>
       <c r="I88" s="13" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4678,217 +4663,217 @@
         <v>118</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D89" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="6" t="s">
         <v>364</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>365</v>
       </c>
       <c r="G89" s="27">
         <v>46240</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="13" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E90" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F90" s="6" t="s">
         <v>367</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>368</v>
       </c>
       <c r="G90" s="27">
         <v>46240</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="13" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E91" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F91" s="6" t="s">
         <v>370</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>371</v>
       </c>
       <c r="G91" s="27">
         <v>46240</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="13" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E92" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F92" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="G92" s="27">
         <v>46240</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="13" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E93" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F93" s="6" t="s">
         <v>376</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="G93" s="27">
         <v>46240</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="13" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E94" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="F94" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>380</v>
       </c>
       <c r="G94" s="27">
         <v>46240</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="13" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E95" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F95" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>383</v>
       </c>
       <c r="G95" s="27">
         <v>46240</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="13" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>312</v>
+        <v>37</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E96" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>386</v>
       </c>
       <c r="G96" s="27">
         <v>46240</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="13" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>118</v>
@@ -4897,25 +4882,25 @@
         <v>37</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E97" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F97" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="G97" s="27">
         <v>46240</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="13" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>118</v>
@@ -4924,52 +4909,52 @@
         <v>37</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E98" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="F98" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="G98" s="27">
         <v>46240</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="13" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E99" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F99" s="6" t="s">
         <v>394</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>395</v>
       </c>
       <c r="G99" s="27">
         <v>46240</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="13" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>118</v>
@@ -4978,79 +4963,79 @@
         <v>10</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E100" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F100" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="G100" s="27">
         <v>46240</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="13" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E101" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F101" s="6" t="s">
         <v>400</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>401</v>
       </c>
       <c r="G101" s="27">
         <v>46240</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="13" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E102" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F102" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="G102" s="27">
         <v>46240</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="13" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>118</v>
@@ -5059,25 +5044,25 @@
         <v>10</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E103" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F103" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>407</v>
       </c>
       <c r="G103" s="27">
         <v>46240</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="13" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>118</v>
@@ -5086,25 +5071,25 @@
         <v>10</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E104" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F104" s="6" t="s">
         <v>409</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>410</v>
       </c>
       <c r="G104" s="27">
         <v>46240</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="13" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>118</v>
@@ -5113,52 +5098,52 @@
         <v>10</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E105" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F105" s="6" t="s">
         <v>412</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>413</v>
       </c>
       <c r="G105" s="27">
         <v>46240</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="13" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E106" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F106" s="6" t="s">
         <v>415</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>416</v>
       </c>
       <c r="G106" s="27">
         <v>46240</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="13" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>118</v>
@@ -5167,25 +5152,25 @@
         <v>15</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E107" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F107" s="6" t="s">
         <v>418</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>419</v>
       </c>
       <c r="G107" s="27">
         <v>46240</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="13" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>118</v>
@@ -5194,25 +5179,25 @@
         <v>15</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E108" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F108" s="6" t="s">
         <v>421</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>422</v>
       </c>
       <c r="G108" s="27">
         <v>46240</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="13" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>118</v>
@@ -5221,25 +5206,25 @@
         <v>15</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E109" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F109" s="6" t="s">
         <v>424</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>425</v>
       </c>
       <c r="G109" s="27">
         <v>46240</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="13" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>118</v>
@@ -5248,25 +5233,25 @@
         <v>15</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E110" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="F110" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="G110" s="27">
         <v>46240</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="13" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>118</v>
@@ -5275,131 +5260,133 @@
         <v>15</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E111" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F111" s="6" t="s">
         <v>430</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>431</v>
       </c>
       <c r="G111" s="27">
         <v>46240</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="13" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E112" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F112" s="6" t="s">
         <v>433</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>434</v>
       </c>
       <c r="G112" s="27">
         <v>46240</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="13" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="10" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="B113" s="3" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="G113" s="27">
-        <v>46240</v>
-      </c>
-      <c r="H113" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G113" s="12">
+        <v>46325</v>
+      </c>
       <c r="I113" s="13" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C114" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="10" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="10" t="s">
+      <c r="E114" s="28" t="s">
+        <v>567</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="G114" s="21">
+        <v>46325</v>
+      </c>
+      <c r="I114" s="22" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C115" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="F115" s="10" t="s">
         <v>570</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D114" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="F114" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G114" s="12">
-        <v>46325</v>
-      </c>
-      <c r="I114" s="13" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="C115" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D115" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="E115" s="28" t="s">
-        <v>572</v>
-      </c>
-      <c r="F115" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="G115" s="21">
         <v>46325</v>
       </c>
+      <c r="H115" s="19" t="s">
+        <v>154</v>
+      </c>
       <c r="I115" s="22" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>133</v>
@@ -5408,74 +5395,45 @@
         <v>15</v>
       </c>
       <c r="D116" s="20" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G116" s="21">
         <v>46325</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I116" s="22" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="10" t="s">
-        <v>581</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C117" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D117" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="E117" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="F117" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="G117" s="21">
-        <v>46325</v>
-      </c>
-      <c r="H117" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I117" s="22" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C118" s="14"/>
-      <c r="D118" s="15"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
-      <c r="H118" s="16"/>
-      <c r="I118" s="17"/>
-      <c r="J118" s="14"/>
-      <c r="K118" s="18"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C122" s="14"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
-      <c r="H122" s="16"/>
-      <c r="I122" s="17"/>
-      <c r="J122" s="14"/>
-      <c r="K122" s="18"/>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C117" s="14"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="16"/>
+      <c r="I117" s="17"/>
+      <c r="J117" s="14"/>
+      <c r="K117" s="18"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C121" s="14"/>
+      <c r="D121" s="15"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="16"/>
+      <c r="I121" s="17"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5491,14 +5449,14 @@
     <hyperlink ref="H25" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="H35" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="F36" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F46" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F57" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F59" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H65" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F67" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F80" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F112" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F114" r:id="rId20" xr:uid="{953294BB-3C86-4D6A-AF5A-9B34E0C7235C}"/>
+    <hyperlink ref="F45" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F56" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F58" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H64" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F66" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F79" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F111" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F113" r:id="rId20" xr:uid="{953294BB-3C86-4D6A-AF5A-9B34E0C7235C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5517,7 +5475,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5525,42 +5483,42 @@
     </row>
     <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5568,37 +5526,37 @@
     </row>
     <row r="12" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
